--- a/public/samples/spws/ptfetape.xlsx
+++ b/public/samples/spws/ptfetape.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/kho SPW/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CE9597-98F3-0748-9D8D-C5C75E88313B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{5C368F4D-CD4D-3B45-9E22-691D764182ED}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="65">
   <si>
     <t>Tồn</t>
   </si>
@@ -55,6 +44,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>EP 030 080 150</t>
@@ -222,30 +214,371 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="#,##0.0"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -253,29 +586,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -324,7 +943,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -357,26 +976,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -409,23 +1011,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -567,31 +1152,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C526CD1-9385-6846-BB72-03B45DBE266C}">
-  <dimension ref="A1:K33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <cols>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="F1" s="1"/>
-      <c r="I1" s="2"/>
+    <row r="1" spans="6:10">
+      <c r="F1" s="4"/>
+      <c r="I1" s="5"/>
       <c r="J1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -607,7 +1187,7 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G2" t="s">
@@ -616,25 +1196,28 @@
       <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D3">
         <v>15</v>
@@ -642,32 +1225,32 @@
       <c r="E3">
         <v>6</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="4">
         <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I3" s="5"/>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -675,32 +1258,32 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="4">
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I4" s="5"/>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D5">
         <v>6.6</v>
@@ -708,32 +1291,32 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="4">
         <v>6.6</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I5" s="5"/>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="4">
         <v>6.6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -741,32 +1324,32 @@
       <c r="E6">
         <v>31</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="4">
         <v>310</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I6" s="5"/>
       <c r="J6">
         <v>7</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="4">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -774,32 +1357,32 @@
       <c r="E7">
         <v>8</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="4">
         <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I7" s="5"/>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -807,32 +1390,32 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I8" s="5"/>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -840,32 +1423,32 @@
       <c r="E9">
         <v>20</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="4">
         <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I9" s="5"/>
       <c r="J9">
         <v>7</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="4">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -873,32 +1456,32 @@
       <c r="E10">
         <v>5</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="4">
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I10" s="5"/>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>31</v>
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -906,32 +1489,32 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="4">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I11" s="5"/>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K11" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -939,32 +1522,32 @@
       <c r="E12">
         <v>26</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="4">
         <v>208</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I12" s="5"/>
       <c r="J12">
         <v>26</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="4">
         <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -972,32 +1555,32 @@
       <c r="E13">
         <v>30</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="4">
         <v>240</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I13" s="5"/>
       <c r="J13">
         <v>12</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="4">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>37</v>
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1005,32 +1588,32 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="4">
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I14" s="5"/>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1038,32 +1621,32 @@
       <c r="E15">
         <v>2</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="4">
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I15" s="5"/>
       <c r="J15">
         <v>2</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1071,32 +1654,32 @@
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="4">
         <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I16" s="5"/>
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1104,32 +1687,32 @@
       <c r="E17">
         <v>2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="4">
         <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I17" s="5"/>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K17" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -1137,32 +1720,32 @@
       <c r="E18">
         <v>2</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="4">
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I18" s="5"/>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -1170,32 +1753,32 @@
       <c r="E19">
         <v>2</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="4">
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I19" s="5"/>
       <c r="J19">
         <v>2</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -1203,236 +1786,236 @@
       <c r="E20">
         <v>6</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="4">
         <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I20" s="5"/>
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="K20" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="4">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2">
         <v>5</v>
       </c>
       <c r="E21">
         <v>6</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="4">
         <v>30</v>
       </c>
       <c r="G21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21">
+        <v>5</v>
+      </c>
+      <c r="K21" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H21" t="s">
+      <c r="D22" s="2">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22">
+        <v>5</v>
+      </c>
+      <c r="K22" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="3" t="s">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="4">
-        <v>5</v>
-      </c>
-      <c r="E22">
-        <v>5</v>
-      </c>
-      <c r="F22" s="1">
-        <v>25</v>
-      </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22">
-        <v>5</v>
-      </c>
-      <c r="K22" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>50</v>
-      </c>
       <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="5">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="3">
         <v>1.8</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="4">
         <v>1.8</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="I23" s="5"/>
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="4">
         <v>1.8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="5">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="3">
         <v>10</v>
       </c>
       <c r="E24">
         <v>10</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="4">
         <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="2">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5">
         <v>44414</v>
       </c>
       <c r="J24">
         <v>2</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="5">
+        <v>12</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="3">
         <v>5</v>
       </c>
       <c r="E25">
         <v>20</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="4">
         <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="2">
+        <v>15</v>
+      </c>
+      <c r="I25" s="5">
         <v>44414</v>
       </c>
       <c r="J25">
         <v>8</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="5">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="3">
         <v>5</v>
       </c>
       <c r="E26">
         <v>10</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="4">
         <v>50</v>
       </c>
       <c r="G26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="2">
+        <v>15</v>
+      </c>
+      <c r="I26" s="5">
         <v>44414</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -1440,34 +2023,34 @@
       <c r="E27">
         <v>20</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="4">
         <v>200</v>
       </c>
       <c r="G27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="2">
+        <v>15</v>
+      </c>
+      <c r="I27" s="5">
         <v>44503</v>
       </c>
       <c r="J27">
         <v>15</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="4">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -1475,34 +2058,34 @@
       <c r="E28">
         <v>10</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="4">
         <v>80</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="2">
+        <v>15</v>
+      </c>
+      <c r="I28" s="5">
         <v>44503</v>
       </c>
       <c r="J28">
         <v>10</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28" s="4">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -1510,34 +2093,34 @@
       <c r="E29">
         <v>20</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="4">
         <v>160</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="2">
+        <v>15</v>
+      </c>
+      <c r="I29" s="5">
         <v>44503</v>
       </c>
       <c r="J29">
         <v>2</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -1545,34 +2128,34 @@
       <c r="E30">
         <v>20</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="4">
         <v>300</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="2">
+        <v>15</v>
+      </c>
+      <c r="I30" s="5">
         <v>44503</v>
       </c>
       <c r="J30">
         <v>15</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="4">
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -1580,34 +2163,34 @@
       <c r="E31">
         <v>20</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="4">
         <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="2">
+        <v>15</v>
+      </c>
+      <c r="I31" s="5">
         <v>44503</v>
       </c>
       <c r="J31">
         <v>13</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K31" s="4">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>58</v>
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -1615,34 +2198,34 @@
       <c r="E32">
         <v>20</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="4">
         <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="2">
+        <v>15</v>
+      </c>
+      <c r="I32" s="5">
         <v>44503</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1650,26 +2233,27 @@
       <c r="E33">
         <v>100</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="4">
         <v>500</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="2">
+        <v>15</v>
+      </c>
+      <c r="I33" s="5">
         <v>44537</v>
       </c>
       <c r="J33">
         <v>2</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K33" s="4">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>